--- a/docs/cyberdrome_teile.xlsx
+++ b/docs/cyberdrome_teile.xlsx
@@ -448,8 +448,8 @@
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 1×HP · 6×ATK · 8×DEF · 3×SPD · 4×MOV · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 1×HP · 6×ATK · 8×DEF · 3×SPD · 4×MOV · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
   </commentList>
@@ -518,8 +518,8 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 1×HP · 8×DEF · 3×SPD · 4×MOV · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 1×HP · 8×DEF · 3×SPD · 4×MOV · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
@@ -606,8 +606,8 @@
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 1×HP · 6×ATK · 8×DEF · 3×SPD · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 1×HP · 6×ATK · 8×DEF · 3×SPD · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
@@ -700,8 +700,8 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 8×DEF · 3×SPD · 4×MOV. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 8×DEF · 3×SPD · 4×MOV. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
@@ -764,8 +764,8 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 6×ATK · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 6×ATK · 0.5×EN max. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -882,14 +882,14 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>Threat als staerkste Waffe
-Zusatzbeitrag zum Threat Score -- aber nur fuer die staerkste Waffe eines Aufbaus, nicht fuer jede. Deshalb steht der Wert neben dem Threat-Beitrag und nicht darin.</t>
+        <t>Kampfwert als staerkste Waffe
+Zusatzbeitrag zum Kampfwert -- aber nur fuer die staerkste Waffe eines Aufbaus, nicht fuer jede. Deshalb steht der Wert neben dem Kampfwert-Beitrag und nicht darin.</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
@@ -1000,8 +1000,8 @@
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>Threat-Beitrag
-Beitrag zum Threat Score aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
+        <t>Kampfwert-Beitrag
+Beitrag zum Kampfwert aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
@@ -1303,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2084,7 +2084,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>• Gewichtung aus DromeBuild.threat_score(): 1 × HP + 6 × ATK + 8 × DEF + 3 × SPD + 4 × MOV + 0.5 × EN max. Das Spiel benutzt genau diese Zahl, um dem Spielersquad ein gleich starkes Gegnersquad gegenueberzustellen (Chaos-Virus).</t>
+          <t>• Gewichtung aus DromeBuild.power_score(): 1 × HP + 6 × ATK + 8 × DEF + 3 × SPD + 4 × MOV + 0.5 × EN max. Das Spiel benutzt genau diese Zahl, um dem Spielersquad ein gleich starkes Gegnersquad gegenueberzustellen (Chaos-Virus).</t>
         </is>
       </c>
     </row>
@@ -2128,63 +2128,70 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>• Ebenfalls nicht enthalten ist die Aggro. Der Kampfwert sagt, wie stark ein Aufbau IST; die Aggro sagt, wie sehr er einen bestimmten Gegner stoert, und entsteht erst im Gefecht aus Aktionen (scripts/battle/aggro_table.gd). Zwei verschiedene Fragen -- sie hiessen frueher beide „Threat“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Farben</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>schwarz = Fakt aus der Teil-JSON</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>blau hinterlegt = Formel, rechnet aus den Spalten daneben</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
         <is>
           <t>grau = Kennzahl ueber die ganze Spalte</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>hellgrau = Hilfszeile, die die Matrix braucht</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B72:C72"/>
@@ -2193,12 +2200,12 @@
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A58:C58"/>
@@ -2206,6 +2213,7 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A64:C64"/>
+    <mergeCell ref="B74:C74"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="B5:C5"/>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -5084,7 +5092,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -5623,7 +5631,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -6188,7 +6196,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -6735,7 +6743,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -7239,12 +7247,12 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Threat als staerkste Waffe</t>
+          <t>Kampfwert als staerkste Waffe</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
@@ -7983,7 +7991,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Threat-Beitrag</t>
+          <t>Kampfwert-Beitrag</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">

--- a/docs/cyberdrome_teile.xlsx
+++ b/docs/cyberdrome_teile.xlsx
@@ -20,13 +20,13 @@
     <sheet name="Silhouetten" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alle Teile'!$A$4:$W$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alle Teile'!$A$4:$W$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Koerperteile'!$A$4:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Kopfteile'!$A$4:$Q$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fussteile'!$A$4:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Kerne'!$A$4:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ausruestung Waffen'!$A$4:$X$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ausruestung Sonstiges'!$A$4:$W$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ausruestung Waffen'!$A$4:$AA$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ausruestung Sonstiges'!$A$4:$Z$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -870,29 +870,47 @@
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
+        <t>Aggro x
+Wie LAUT die Aktion ist: Multiplikator auf die Aggro, die ihre Wirkung erzeugt. 1.0 ist die Grundlinie, 0.5 Heilung, 0.35 Praezision. Trennt „wie viel Schaden“ von „wie sehr provoziert es“ -- deshalb ueberlebt der Strix in der zweiten Reihe.</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <t>Provokation
+Fuer so viele EIGENE Zuege muss das Ziel den Verursacher angreifen. Der einzige harte Zwang im Spiel, deshalb befristet.</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>Aggro +%
+Wie viel mehr Aufmerksamkeit alles erzeugt, was der Traeger tut -- in Prozentpunkten, additiv ueber alle Teile. Der einzige Weg zu Aggro ohne eigene Aktion, und er kostet einen Ausruestungsslot. Geht NICHT in den Kampfwert ein.</t>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
         <t>Power je EN
 Schaden je Energiepunkt. „kostenlos“ heisst: die Aktion kostet gar keine Energie und laesst sich jeden Zug einsetzen.</t>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>Power je Gewicht
 Schaden je Gewichtspunkt -- die Waehrung, in der die Traglast des Chassis bezahlt wird.</t>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <t>Kampfwert als staerkste Waffe
 Zusatzbeitrag zum Kampfwert -- aber nur fuer die staerkste Waffe eines Aufbaus, nicht fuer jede. Deshalb steht der Wert neben dem Kampfwert-Beitrag und nicht darin.</t>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <t>Kampfwert-Beitrag
 Beitrag zum Kampfwert aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0" shapeId="0">
       <text>
         <t>Silhouetten-Merkmal
 Woran der Spieler das Teil auf dem Feld erkennt. parts/README.md, Abschnitt 6a.</t>
@@ -994,17 +1012,35 @@
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
+        <t>Aggro x
+Wie LAUT die Aktion ist: Multiplikator auf die Aggro, die ihre Wirkung erzeugt. 1.0 ist die Grundlinie, 0.5 Heilung, 0.35 Praezision. Trennt „wie viel Schaden“ von „wie sehr provoziert es“ -- deshalb ueberlebt der Strix in der zweiten Reihe.</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>Provokation
+Fuer so viele EIGENE Zuege muss das Ziel den Verursacher angreifen. Der einzige harte Zwang im Spiel, deshalb befristet.</t>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <t>Aggro +%
+Wie viel mehr Aufmerksamkeit alles erzeugt, was der Traeger tut -- in Prozentpunkten, additiv ueber alle Teile. Der einzige Weg zu Aggro ohne eigene Aktion, und er kostet einen Ausruestungsslot. Geht NICHT in den Kampfwert ein.</t>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
         <t>Wirkung
 Liest die Spalte „Power“: positiv ist Schaden, negativ Heilung, 0 heisst reine Verschiebung oder Status.</t>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <t>Kampfwert-Beitrag
 Beitrag zum Kampfwert aus drome_build.gd: 6×ATK · 8×DEF. Die Werte, die dieser Bauteiltyp gar nicht fuehrt, sind ueberall 0 und stehen deshalb nicht in der Formel. Ueber diese Spalte lassen sich Teile verschiedener Typen vergleichen.</t>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <t>Silhouetten-Merkmal
 Woran der Spieler das Teil auf dem Feld erkennt. parts/README.md, Abschnitt 6a.</t>
@@ -1303,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1494,7 +1530,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('Alle Teile'!$D$5:$D$27,A18)</f>
+        <f>COUNTIF('Alle Teile'!$D$5:$D$28,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1510,7 +1546,7 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('Alle Teile'!$D$5:$D$27,A19)</f>
+        <f>COUNTIF('Alle Teile'!$D$5:$D$28,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -1526,7 +1562,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>COUNTIF('Alle Teile'!$D$5:$D$27,A20)</f>
+        <f>COUNTIF('Alle Teile'!$D$5:$D$28,A20)</f>
         <v/>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1542,7 +1578,7 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF('Alle Teile'!$D$5:$D$27,A21)</f>
+        <f>COUNTIF('Alle Teile'!$D$5:$D$28,A21)</f>
         <v/>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -1558,7 +1594,7 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF('Alle Teile'!$D$5:$D$27,A22)</f>
+        <f>COUNTIF('Alle Teile'!$D$5:$D$28,A22)</f>
         <v/>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1896,295 +1932,346 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>aggro_bonus</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Aggro +%</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Wie viel mehr Aufmerksamkeit alles erzeugt, was der Traeger tut -- in Prozentpunkten, additiv ueber alle Teile. Der einzige Weg zu Aggro ohne eigene Aktion, und er kostet einen Ausruestungsslot. Geht NICHT in den Kampfwert ein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Aktionswerte</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Schaden ist deterministisch -- kein Trefferwurf, kein Krit, keine Ausweichchance (action_data.gd)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Feld in der JSON</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Spalte</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Bedeutung</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>range_tiles</t>
-        </is>
-      </c>
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>Reichweite</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Felder bis zum Ziel.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>aoe_radius</t>
+          <t>range_tiles</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>AoE</t>
+          <t>Reichweite</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Radius um das Ziel. 0 = nur das Ziel selbst.</t>
+          <t>Felder bis zum Ziel.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>en_cost</t>
+          <t>aoe_radius</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>EN-Kosten</t>
+          <t>AoE</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Energie je Einsatz.</t>
+          <t>Radius um das Ziel. 0 = nur das Ziel selbst.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>en_cost</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>EN-Kosten</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Positiv = Schaden, negativ = Heilung. Ein Vorzeichen statt zweier Felder.</t>
+          <t>Energie je Einsatz.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>requires_line_of_sight</t>
+          <t>power</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Sichtlinie</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Braucht freie Sicht zum Ziel.</t>
+          <t>Positiv = Schaden, negativ = Heilung. Ein Vorzeichen statt zweier Felder.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
+          <t>requires_line_of_sight</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Sichtlinie</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Braucht freie Sicht zum Ziel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
           <t>push_tiles</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Schub</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Positiv = wegstossen, negativ = heranziehen.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>aggro_coeff</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Aggro x</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Wie LAUT die Aktion ist: Multiplikator auf die Aggro, die ihre Wirkung erzeugt. 1.0 ist die Grundlinie, 0.5 Heilung, 0.35 Praezision. Trennt „wie viel Schaden“ von „wie sehr provoziert es“ -- deshalb ueberlebt der Strix in der zweiten Reihe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>taunt_turns</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Provokation</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Fuer so viele EIGENE Zuege muss das Ziel den Verursacher angreifen. Der einzige harte Zwang im Spiel, deshalb befristet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Bauregeln</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Was die Werkstatt prueft, bevor ein Aufbau gueltig ist -- DromeBuild.validate()</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>• Chassis, Kopf, Antrieb und Kern sind Pflicht. Ohne eines davon ist der Aufbau ungueltig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>• Mindestens eine Waffe muss bestueckt sein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>• Summe Gewicht darf die Traglast des Chassis nicht ueberschreiten.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>• Summe Energiebedarf darf die Energieabgabe des Kerns nicht ueberschreiten.</t>
+          <t>• Chassis, Kopf, Antrieb und Kern sind Pflicht. Ohne eines davon ist der Aufbau ungueltig.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>• MOV und SPD muessen im fertigen Aufbau mindestens 1 sein -- das Molok-Chassis zieht beide ins Minus und braucht deshalb einen Antrieb, der das auffaengt.</t>
+          <t>• Mindestens eine Waffe muss bestueckt sein.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>• Ein Ausruestungsteil muss die Regel seines Slots erfuellen (Montageklasse und Bauart). Siehe Blatt „Kompatibilitaet“.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Kampfwert-Beitrag</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>die einzige Spalte, die Teile verschiedener Typen vergleichbar macht</t>
+          <t>• Summe Gewicht darf die Traglast des Chassis nicht ueberschreiten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>• Summe Energiebedarf darf die Energieabgabe des Kerns nicht ueberschreiten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>• MOV und SPD muessen im fertigen Aufbau mindestens 1 sein -- das Molok-Chassis zieht beide ins Minus und braucht deshalb einen Antrieb, der das auffaengt.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>• Gewichtung aus DromeBuild.power_score(): 1 × HP + 6 × ATK + 8 × DEF + 3 × SPD + 4 × MOV + 0.5 × EN max. Das Spiel benutzt genau diese Zahl, um dem Spielersquad ein gleich starkes Gegnersquad gegenueberzustellen (Chaos-Virus).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>• Sie ist linear -- der Score eines Aufbaus ist die Summe der Beitraege seiner Teile. Deshalb laesst sich ueber diese eine Spalte ein Kopf mit einem Antrieb vergleichen, obwohl die beiden keinen einzigen Wert gemeinsam haben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>• Auf den Typblaettern stehen in der Formel nur die Werte, die der Typ ueberhaupt fuehrt. Die uebrigen sind dort bei jedem Teil null, das Ergebnis ist also dasselbe -- die Selbstpruefung des Skripts besteht darauf.</t>
+          <t>• Ein Ausruestungsteil muss die Regel seines Slots erfuellen (Montageklasse und Bauart). Siehe Blatt „Kompatibilitaet“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Kampfwert-Beitrag</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>die einzige Spalte, die Teile verschiedener Typen vergleichbar macht</t>
         </is>
       </c>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>• Waffen gehen zusaetzlich mit 2 × Power ein, aber nur die STAERKSTE Waffe eines Aufbaus. Das haengt an der Bestueckung, nicht am Teil, und steht deshalb auf dem Waffenblatt in einer eigenen Spalte daneben.</t>
+          <t>• Gewichtung aus DromeBuild.power_score(): 1 × HP + 6 × ATK + 8 × DEF + 3 × SPD + 4 × MOV + 0.5 × EN max. Das Spiel benutzt genau diese Zahl, um dem Spielersquad ein gleich starkes Gegnersquad gegenueberzustellen (Chaos-Virus).</t>
         </is>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>• Was der Score NICHT abbildet: Reichweite, Traglast, Energiebedarf und alles Gelaende. Ein Antrieb, der Stufen betreten darf, ist dadurch keinen Punkt wert -- im Gefecht aber oft entscheidend.</t>
+          <t>• Sie ist linear -- der Score eines Aufbaus ist die Summe der Beitraege seiner Teile. Deshalb laesst sich ueber diese eine Spalte ein Kopf mit einem Antrieb vergleichen, obwohl die beiden keinen einzigen Wert gemeinsam haben.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>• Auf den Typblaettern stehen in der Formel nur die Werte, die der Typ ueberhaupt fuehrt. Die uebrigen sind dort bei jedem Teil null, das Ergebnis ist also dasselbe -- die Selbstpruefung des Skripts besteht darauf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>• Waffen gehen zusaetzlich mit 2 × Power ein, aber nur die STAERKSTE Waffe eines Aufbaus. Das haengt an der Bestueckung, nicht am Teil, und steht deshalb auf dem Waffenblatt in einer eigenen Spalte daneben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>• Was der Score NICHT abbildet: Reichweite, Traglast, Energiebedarf und alles Gelaende. Ein Antrieb, der Stufen betreten darf, ist dadurch keinen Punkt wert -- im Gefecht aber oft entscheidend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>• Ebenfalls nicht enthalten ist die Aggro. Der Kampfwert sagt, wie stark ein Aufbau IST; die Aggro sagt, wie sehr er einen bestimmten Gegner stoert, und entsteht erst im Gefecht aus Aktionen (scripts/battle/aggro_table.gd). Zwei verschiedene Fragen -- sie hiessen frueher beide „Threat“.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>Farben</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>schwarz = Fakt aus der Teil-JSON</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
         <is>
           <t>blau hinterlegt = Formel, rechnet aus den Spalten daneben</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>grau = Kennzahl ueber die ganze Spalte</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>Beispiel</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>hellgrau = Hilfszeile, die die Matrix braucht</t>
         </is>
@@ -2194,16 +2281,13 @@
   <mergeCells count="26">
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="A71:C71"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B73:C73"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A63:C63"/>
@@ -2212,12 +2296,15 @@
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A64:C64"/>
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="B75:C75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2229,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3011,6 +3098,69 @@
       </c>
       <c r="N16" s="36">
         <f>IF(AND($D16&lt;=N$7,ISNUMBER(SEARCH($E16,N$8)),OR($F16="alle",ISNUMBER(SEARCH(N$5,$F16)))),"ja","–")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>EQP-008</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Koedersender</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>leicht</t>
+        </is>
+      </c>
+      <c r="D17" s="35">
+        <f>MATCH(C17,$B$1:$D$1,0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>alle</t>
+        </is>
+      </c>
+      <c r="G17" s="36">
+        <f>IF(AND($D17&lt;=G$7,ISNUMBER(SEARCH($E17,G$8)),OR($F17="alle",ISNUMBER(SEARCH(G$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="H17" s="36">
+        <f>IF(AND($D17&lt;=H$7,ISNUMBER(SEARCH($E17,H$8)),OR($F17="alle",ISNUMBER(SEARCH(H$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="I17" s="36">
+        <f>IF(AND($D17&lt;=I$7,ISNUMBER(SEARCH($E17,I$8)),OR($F17="alle",ISNUMBER(SEARCH(I$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="J17" s="36">
+        <f>IF(AND($D17&lt;=J$7,ISNUMBER(SEARCH($E17,J$8)),OR($F17="alle",ISNUMBER(SEARCH(J$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="K17" s="36">
+        <f>IF(AND($D17&lt;=K$7,ISNUMBER(SEARCH($E17,K$8)),OR($F17="alle",ISNUMBER(SEARCH(K$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="L17" s="36">
+        <f>IF(AND($D17&lt;=L$7,ISNUMBER(SEARCH($E17,L$8)),OR($F17="alle",ISNUMBER(SEARCH(L$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="M17" s="36">
+        <f>IF(AND($D17&lt;=M$7,ISNUMBER(SEARCH($E17,M$8)),OR($F17="alle",ISNUMBER(SEARCH(M$5,$F17)))),"ja","–")</f>
+        <v/>
+      </c>
+      <c r="N17" s="36">
+        <f>IF(AND($D17&lt;=N$7,ISNUMBER(SEARCH($E17,N$8)),OR($F17="alle",ISNUMBER(SEARCH(N$5,$F17)))),"ja","–")</f>
         <v/>
       </c>
     </row>
@@ -3437,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3693,7 +3843,7 @@
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n"/>
       <c r="P6" s="17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="17" t="n"/>
       <c r="R6" s="7" t="inlineStr"/>
@@ -4972,9 +5122,77 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>EQP-008</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Koedersender</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>HX-Molok // Juggernaut</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Ausruestung</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>leicht</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="17" t="n"/>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" s="17" t="n"/>
+      <c r="Q28" s="17" t="n"/>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>Stoersignal</t>
+        </is>
+      </c>
+      <c r="S28" s="17" t="n"/>
+      <c r="T28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="V28" s="18">
+        <f>G28*1+L28*6+M28*8+J28*3+K28*4+H28*0.5</f>
+        <v/>
+      </c>
+      <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>support, beacon, aggro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:W27"/>
-  <conditionalFormatting sqref="V5:V27">
+  <autoFilter ref="A4:W28"/>
+  <conditionalFormatting sqref="V5:V28">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -5213,7 +5431,7 @@
         <v>-1</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J6" s="17" t="n">
         <v>0</v>
@@ -7106,7 +7324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7126,13 +7344,16 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7237,35 +7458,50 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
+          <t>Aggro x</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Provokation</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Aggro +%</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>Power je EN</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Power je Gewicht</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>Kampfwert als staerkste Waffe</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Kampfwert-Beitrag</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Silhouetten-Merkmal</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>sagt dem Spieler</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
@@ -7339,33 +7575,42 @@
       <c r="Q5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="14">
         <f>IF(O5=0,"kostenlos",ROUND(L5/O5,1))</f>
         <v/>
       </c>
-      <c r="S5" s="18">
+      <c r="V5" s="18">
         <f>ROUND(L5/F5,1)</f>
         <v/>
       </c>
-      <c r="T5" s="18">
+      <c r="W5" s="18">
         <f>L5*2</f>
         <v/>
       </c>
-      <c r="U5" s="18">
+      <c r="X5" s="18">
         <f>H5*6+I5*8</f>
         <v/>
       </c>
-      <c r="V5" s="9" t="inlineStr">
+      <c r="Y5" s="9" t="inlineStr">
         <is>
           <t>ein glattes Rohr, sonst nichts</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="Z5" s="9" t="inlineStr">
         <is>
           <t>leicht, kurze Reichweite</t>
         </is>
       </c>
-      <c r="X5" s="7" t="inlineStr">
+      <c r="AA5" s="7" t="inlineStr">
         <is>
           <t>weapon, ranged</t>
         </is>
@@ -7439,33 +7684,42 @@
       <c r="Q6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="14">
+      <c r="R6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="14">
         <f>IF(O6=0,"kostenlos",ROUND(L6/O6,1))</f>
         <v/>
       </c>
-      <c r="S6" s="18">
+      <c r="V6" s="18">
         <f>ROUND(L6/F6,1)</f>
         <v/>
       </c>
-      <c r="T6" s="18">
+      <c r="W6" s="18">
         <f>L6*2</f>
         <v/>
       </c>
-      <c r="U6" s="18">
+      <c r="X6" s="18">
         <f>H6*6+I6*8</f>
         <v/>
       </c>
-      <c r="V6" s="9" t="inlineStr">
+      <c r="Y6" s="9" t="inlineStr">
         <is>
           <t>Muendungsbremse mit Querfluegeln, Trommelmagazin, Abstuetzstrebe</t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="Z6" s="9" t="inlineStr">
         <is>
           <t>schwer, abgestuetzt -- Artillerie</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="AA6" s="7" t="inlineStr">
         <is>
           <t>weapon, heavy</t>
         </is>
@@ -7539,33 +7793,42 @@
       <c r="Q7" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="14">
         <f>IF(O7=0,"kostenlos",ROUND(L7/O7,1))</f>
         <v/>
       </c>
-      <c r="S7" s="18">
+      <c r="V7" s="18">
         <f>ROUND(L7/F7,1)</f>
         <v/>
       </c>
-      <c r="T7" s="18">
+      <c r="W7" s="18">
         <f>L7*2</f>
         <v/>
       </c>
-      <c r="U7" s="18">
+      <c r="X7" s="18">
         <f>H7*6+I7*8</f>
         <v/>
       </c>
-      <c r="V7" s="9" t="inlineStr">
+      <c r="Y7" s="9" t="inlineStr">
         <is>
           <t>langer duenner Stab mit Kopfglut</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="Z7" s="9" t="inlineStr">
         <is>
           <t>arkane Waffe</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="AA7" s="7" t="inlineStr">
         <is>
           <t>weapon, arcane, round</t>
         </is>
@@ -7639,33 +7902,42 @@
       <c r="Q8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="14">
         <f>IF(O8=0,"kostenlos",ROUND(L8/O8,1))</f>
         <v/>
       </c>
-      <c r="S8" s="18">
+      <c r="V8" s="18">
         <f>ROUND(L8/F8,1)</f>
         <v/>
       </c>
-      <c r="T8" s="18">
+      <c r="W8" s="18">
         <f>L8*2</f>
         <v/>
       </c>
-      <c r="U8" s="18">
+      <c r="X8" s="18">
         <f>H8*6+I8*8</f>
         <v/>
       </c>
-      <c r="V8" s="9" t="inlineStr">
+      <c r="Y8" s="9" t="inlineStr">
         <is>
           <t>ueberlanger duenner Doppellauf, Zielblock, Gabel</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="Z8" s="9" t="inlineStr">
         <is>
           <t>Praezision, grosse Reichweite</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="AA8" s="7" t="inlineStr">
         <is>
           <t>weapon, heavy, sniper</t>
         </is>
@@ -7714,16 +7986,16 @@
         <f>MIN(O5:O8)</f>
         <v/>
       </c>
-      <c r="S10" s="21">
-        <f>MIN(S5:S8)</f>
-        <v/>
-      </c>
-      <c r="T10" s="21">
-        <f>MIN(T5:T8)</f>
-        <v/>
-      </c>
-      <c r="U10" s="21">
-        <f>MIN(U5:U8)</f>
+      <c r="V10" s="21">
+        <f>MIN(V5:V8)</f>
+        <v/>
+      </c>
+      <c r="W10" s="21">
+        <f>MIN(W5:W8)</f>
+        <v/>
+      </c>
+      <c r="X10" s="21">
+        <f>MIN(X5:X8)</f>
         <v/>
       </c>
     </row>
@@ -7765,16 +8037,16 @@
         <f>AVERAGE(O5:O8)</f>
         <v/>
       </c>
-      <c r="S11" s="21">
-        <f>AVERAGE(S5:S8)</f>
-        <v/>
-      </c>
-      <c r="T11" s="21">
-        <f>AVERAGE(T5:T8)</f>
-        <v/>
-      </c>
-      <c r="U11" s="21">
-        <f>AVERAGE(U5:U8)</f>
+      <c r="V11" s="21">
+        <f>AVERAGE(V5:V8)</f>
+        <v/>
+      </c>
+      <c r="W11" s="21">
+        <f>AVERAGE(W5:W8)</f>
+        <v/>
+      </c>
+      <c r="X11" s="21">
+        <f>AVERAGE(X5:X8)</f>
         <v/>
       </c>
     </row>
@@ -7816,22 +8088,22 @@
         <f>MAX(O5:O8)</f>
         <v/>
       </c>
-      <c r="S12" s="21">
-        <f>MAX(S5:S8)</f>
-        <v/>
-      </c>
-      <c r="T12" s="21">
-        <f>MAX(T5:T8)</f>
-        <v/>
-      </c>
-      <c r="U12" s="21">
-        <f>MAX(U5:U8)</f>
+      <c r="V12" s="21">
+        <f>MAX(V5:V8)</f>
+        <v/>
+      </c>
+      <c r="W12" s="21">
+        <f>MAX(W5:W8)</f>
+        <v/>
+      </c>
+      <c r="X12" s="21">
+        <f>MAX(X5:X8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X8"/>
-  <conditionalFormatting sqref="U5:U8">
+  <autoFilter ref="A4:AA8"/>
+  <conditionalFormatting sqref="X5:X8">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -7851,7 +8123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7872,11 +8144,14 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7986,25 +8261,40 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t>Aggro x</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Provokation</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Aggro +%</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
           <t>Wirkung</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>Kampfwert-Beitrag</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Silhouetten-Merkmal</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>sagt dem Spieler</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
@@ -8065,25 +8355,30 @@
       <c r="P5" s="17" t="n"/>
       <c r="Q5" s="7" t="n"/>
       <c r="R5" s="17" t="n"/>
-      <c r="S5" s="14">
+      <c r="S5" s="17" t="n"/>
+      <c r="T5" s="17" t="n"/>
+      <c r="U5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="14">
         <f>IF(K5="—","passiv",IF(M5&lt;0,"Heilung "&amp;ABS(M5),IF(M5=0,"kein Schaden","Schaden "&amp;M5)))</f>
         <v/>
       </c>
-      <c r="T5" s="18">
+      <c r="W5" s="18">
         <f>I5*6+J5*8</f>
         <v/>
       </c>
-      <c r="U5" s="9" t="inlineStr">
+      <c r="X5" s="9" t="inlineStr">
         <is>
           <t>flache Wand quer zur Blickrichtung</t>
         </is>
       </c>
-      <c r="V5" s="9" t="inlineStr">
+      <c r="Y5" s="9" t="inlineStr">
         <is>
           <t>Deckung</t>
         </is>
       </c>
-      <c r="W5" s="7" t="inlineStr">
+      <c r="Z5" s="7" t="inlineStr">
         <is>
           <t>defense</t>
         </is>
@@ -8162,25 +8457,34 @@
       <c r="R6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="14">
         <f>IF(K6="—","passiv",IF(M6&lt;0,"Heilung "&amp;ABS(M6),IF(M6=0,"kein Schaden","Schaden "&amp;M6)))</f>
         <v/>
       </c>
-      <c r="T6" s="18">
+      <c r="W6" s="18">
         <f>I6*6+J6*8</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="X6" s="9" t="inlineStr">
         <is>
           <t>flacher Pod auf der Schulterbruecke</t>
         </is>
       </c>
-      <c r="V6" s="9" t="inlineStr">
+      <c r="Y6" s="9" t="inlineStr">
         <is>
           <t>Support, keine Waffe</t>
         </is>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="Z6" s="7" t="inlineStr">
         <is>
           <t>support, shoulder</t>
         </is>
@@ -8259,167 +8563,282 @@
       <c r="R7" s="17" t="n">
         <v>-2</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="14">
         <f>IF(K7="—","passiv",IF(M7&lt;0,"Heilung "&amp;ABS(M7),IF(M7=0,"kein Schaden","Schaden "&amp;M7)))</f>
         <v/>
       </c>
-      <c r="T7" s="18">
+      <c r="W7" s="18">
         <f>I7*6+J7*8</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="X7" s="9" t="inlineStr">
         <is>
           <t>schwebender Ring vor der Hand</t>
         </is>
       </c>
-      <c r="V7" s="9" t="inlineStr">
+      <c r="Y7" s="9" t="inlineStr">
         <is>
           <t>Support, arkan</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>support, arcane, round</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahlen ueber die Zeilen darueber -- Formeln, keine festen Zahlen</t>
-        </is>
-      </c>
-      <c r="G9" s="20">
-        <f>MIN(G5:G7)</f>
-        <v/>
-      </c>
-      <c r="H9" s="20">
-        <f>MIN(H5:H7)</f>
-        <v/>
-      </c>
-      <c r="I9" s="20">
-        <f>MIN(I5:I7)</f>
-        <v/>
-      </c>
-      <c r="J9" s="20">
-        <f>MIN(J5:J7)</f>
-        <v/>
-      </c>
-      <c r="M9" s="20">
-        <f>MIN(M5:M7)</f>
-        <v/>
-      </c>
-      <c r="N9" s="20">
-        <f>MIN(N5:N7)</f>
-        <v/>
-      </c>
-      <c r="O9" s="20">
-        <f>MIN(O5:O7)</f>
-        <v/>
-      </c>
-      <c r="P9" s="20">
-        <f>MIN(P5:P7)</f>
-        <v/>
-      </c>
-      <c r="T9" s="21">
-        <f>MIN(T5:T7)</f>
-        <v/>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>EQP-008</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Koedersender</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>HX-Molok // Juggernaut</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>eq_bait_beacon</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>leicht</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Stoersignal</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Einzelziel</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V8" s="14">
+        <f>IF(K8="—","passiv",IF(M8&lt;0,"Heilung "&amp;ABS(M8),IF(M8=0,"kein Schaden","Schaden "&amp;M8)))</f>
+        <v/>
+      </c>
+      <c r="W8" s="18">
+        <f>I8*6+J8*8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>duenner Mast ueber Kopfhoehe, drei waagerechte Sendeschirme, Gegengewicht hinten-unten</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="inlineStr">
+        <is>
+          <t>laut und unbewaffnet -- zieht Aufmerksamkeit und provoziert</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
+          <t>support, beacon, aggro</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Mittel</t>
-        </is>
-      </c>
-      <c r="G10" s="21">
-        <f>AVERAGE(G5:G7)</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>AVERAGE(H5:H7)</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>AVERAGE(I5:I7)</f>
-        <v/>
-      </c>
-      <c r="J10" s="21">
-        <f>AVERAGE(J5:J7)</f>
-        <v/>
-      </c>
-      <c r="M10" s="21">
-        <f>AVERAGE(M5:M7)</f>
-        <v/>
-      </c>
-      <c r="N10" s="21">
-        <f>AVERAGE(N5:N7)</f>
-        <v/>
-      </c>
-      <c r="O10" s="21">
-        <f>AVERAGE(O5:O7)</f>
-        <v/>
-      </c>
-      <c r="P10" s="21">
-        <f>AVERAGE(P5:P7)</f>
-        <v/>
-      </c>
-      <c r="T10" s="21">
-        <f>AVERAGE(T5:T7)</f>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahlen ueber die Zeilen darueber -- Formeln, keine festen Zahlen</t>
+        </is>
+      </c>
+      <c r="G10" s="20">
+        <f>MIN(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H10" s="20">
+        <f>MIN(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I10" s="20">
+        <f>MIN(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J10" s="20">
+        <f>MIN(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="M10" s="20">
+        <f>MIN(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N10" s="20">
+        <f>MIN(N5:N8)</f>
+        <v/>
+      </c>
+      <c r="O10" s="20">
+        <f>MIN(O5:O8)</f>
+        <v/>
+      </c>
+      <c r="P10" s="20">
+        <f>MIN(P5:P8)</f>
+        <v/>
+      </c>
+      <c r="W10" s="21">
+        <f>MIN(W5:W8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="G11" s="21">
+        <f>AVERAGE(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>AVERAGE(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>AVERAGE(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>AVERAGE(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
+        <f>AVERAGE(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>AVERAGE(N5:N8)</f>
+        <v/>
+      </c>
+      <c r="O11" s="21">
+        <f>AVERAGE(O5:O8)</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>AVERAGE(P5:P8)</f>
+        <v/>
+      </c>
+      <c r="W11" s="21">
+        <f>AVERAGE(W5:W8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
           <t>Maximum</t>
         </is>
       </c>
-      <c r="G11" s="20">
-        <f>MAX(G5:G7)</f>
-        <v/>
-      </c>
-      <c r="H11" s="20">
-        <f>MAX(H5:H7)</f>
-        <v/>
-      </c>
-      <c r="I11" s="20">
-        <f>MAX(I5:I7)</f>
-        <v/>
-      </c>
-      <c r="J11" s="20">
-        <f>MAX(J5:J7)</f>
-        <v/>
-      </c>
-      <c r="M11" s="20">
-        <f>MAX(M5:M7)</f>
-        <v/>
-      </c>
-      <c r="N11" s="20">
-        <f>MAX(N5:N7)</f>
-        <v/>
-      </c>
-      <c r="O11" s="20">
-        <f>MAX(O5:O7)</f>
-        <v/>
-      </c>
-      <c r="P11" s="20">
-        <f>MAX(P5:P7)</f>
-        <v/>
-      </c>
-      <c r="T11" s="21">
-        <f>MAX(T5:T7)</f>
+      <c r="G12" s="20">
+        <f>MAX(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H12" s="20">
+        <f>MAX(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I12" s="20">
+        <f>MAX(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J12" s="20">
+        <f>MAX(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="M12" s="20">
+        <f>MAX(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N12" s="20">
+        <f>MAX(N5:N8)</f>
+        <v/>
+      </c>
+      <c r="O12" s="20">
+        <f>MAX(O5:O8)</f>
+        <v/>
+      </c>
+      <c r="P12" s="20">
+        <f>MAX(P5:P8)</f>
+        <v/>
+      </c>
+      <c r="W12" s="21">
+        <f>MAX(W5:W8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:W7"/>
-  <conditionalFormatting sqref="T5:T7">
+  <autoFilter ref="A4:Z8"/>
+  <conditionalFormatting sqref="W5:W8">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
